--- a/artfynd/A 40718-2025 artfynd.xlsx
+++ b/artfynd/A 40718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119022707</v>
+        <v>119022718</v>
       </c>
       <c r="B2" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tallbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>729683</v>
+        <v>729769</v>
       </c>
       <c r="R2" t="n">
-        <v>7218469</v>
+        <v>7218520</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119022708</v>
+        <v>119022719</v>
       </c>
       <c r="B3" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>729681</v>
+        <v>729769</v>
       </c>
       <c r="R3" t="n">
-        <v>7218465</v>
+        <v>7218520</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119022715</v>
+        <v>119022708</v>
       </c>
       <c r="B4" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tallbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>729704</v>
+        <v>729681</v>
       </c>
       <c r="R4" t="n">
-        <v>7218513</v>
+        <v>7218465</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119022719</v>
+        <v>119022705</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729769</v>
+        <v>729671</v>
       </c>
       <c r="R5" t="n">
-        <v>7218520</v>
+        <v>7218440</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,44 +1096,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119022716</v>
+        <v>119022717</v>
       </c>
       <c r="B6" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729745</v>
+        <v>729744</v>
       </c>
       <c r="R6" t="n">
-        <v>7218535</v>
+        <v>7218536</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119022709</v>
+        <v>119022713</v>
       </c>
       <c r="B7" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729698</v>
+        <v>729699</v>
       </c>
       <c r="R7" t="n">
-        <v>7218484</v>
+        <v>7218503</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119022711</v>
+        <v>119022712</v>
       </c>
       <c r="B8" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729701</v>
+        <v>729699</v>
       </c>
       <c r="R8" t="n">
-        <v>7218506</v>
+        <v>7218503</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119022703</v>
+        <v>119022707</v>
       </c>
       <c r="B9" t="n">
-        <v>96837</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tallbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729732</v>
+        <v>729683</v>
       </c>
       <c r="R9" t="n">
-        <v>7218403</v>
+        <v>7218469</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,15 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119022705</v>
+        <v>119022704</v>
       </c>
       <c r="B10" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,24 +1547,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tallbergsmyran, Vb</t>
@@ -1693,50 +1648,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119022713</v>
+        <v>119022715</v>
       </c>
       <c r="B11" t="n">
-        <v>79621</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tallbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729699</v>
+        <v>729704</v>
       </c>
       <c r="R11" t="n">
-        <v>7218503</v>
+        <v>7218513</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119022717</v>
+        <v>119022703</v>
       </c>
       <c r="B12" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729744</v>
+        <v>729732</v>
       </c>
       <c r="R12" t="n">
-        <v>7218536</v>
+        <v>7218403</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,44 +1860,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119022718</v>
+        <v>119022711</v>
       </c>
       <c r="B13" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729769</v>
+        <v>729701</v>
       </c>
       <c r="R13" t="n">
-        <v>7218520</v>
+        <v>7218506</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,239 +1967,10 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>119022712</v>
-      </c>
-      <c r="B14" t="n">
-        <v>79627</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tallbergsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>729699</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7218503</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>119022704</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tallbergsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>729671</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7218440</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Norsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
